--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98600590</v>
+        <v>136980670</v>
       </c>
       <c r="B2" t="n">
-        <v>93197</v>
+        <v>92381</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Smedjebacken, Dlr</t>
+          <t>Dövensberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536367</v>
+        <v>536189</v>
       </c>
       <c r="R2" t="n">
-        <v>6671836</v>
+        <v>6671740</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-11-18</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,55 +762,81 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Populus tremula</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sofia Berg</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sofia Berg, Anders Esplund</t>
+          <t>Janolof Hermansson, Stig-Åke Svenson, Cecilia Rastad, Åke Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98600590</t>
+          <t>https://artportalen.se/Sighting/136980670</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98600589</v>
+        <v>98600590</v>
       </c>
       <c r="B3" t="n">
-        <v>99035</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536348</v>
+        <v>536367</v>
       </c>
       <c r="R3" t="n">
-        <v>6671865</v>
+        <v>6671836</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,16 +907,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98600589</t>
+          <t>https://artportalen.se/Sighting/98600590</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98600591</v>
+        <v>136980386</v>
       </c>
       <c r="B4" t="n">
-        <v>97983</v>
+        <v>81134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +924,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6444</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skriftlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Graphis scripta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Smedjebacken, Dlr</t>
+          <t>Dövensberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536381</v>
+        <v>535870</v>
       </c>
       <c r="R4" t="n">
-        <v>6671830</v>
+        <v>6672073</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +981,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-11-18</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,33 +995,59 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Kärr med lövträd</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>gammal 40 cm diam</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa # gammal 40 cm diam</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sofia Berg</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sofia Berg, Anders Esplund</t>
+          <t>Janolof Hermansson, Stig-Åke Svenson, Cecilia Rastad, Åke Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98600591</t>
+          <t>https://artportalen.se/Sighting/136980386</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98600592</v>
+        <v>136980140</v>
       </c>
       <c r="B5" t="n">
-        <v>97983</v>
+        <v>79732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,37 +1055,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6459</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Smedjebacken, Dlr</t>
+          <t>Dövensberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536385</v>
+        <v>535927</v>
       </c>
       <c r="R5" t="n">
-        <v>6671884</v>
+        <v>6672084</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1112,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-11-18</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1065,33 +1126,59 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>örtrikt nedanför brant med mossiga klippor</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>skogslind</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Tilia cordata</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Tilia cordata</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sofia Berg</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sofia Berg, Anders Esplund</t>
+          <t>Janolof Hermansson, Stig-Åke Svenson, Cecilia Rastad, Åke Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98600592</t>
+          <t>https://artportalen.se/Sighting/136980140</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98600593</v>
+        <v>136980578</v>
       </c>
       <c r="B6" t="n">
-        <v>97983</v>
+        <v>79732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,37 +1186,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6459</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Smedjebacken, Dlr</t>
+          <t>Dövensberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536389</v>
+        <v>535876</v>
       </c>
       <c r="R6" t="n">
-        <v>6671850</v>
+        <v>6671955</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,38 +1243,2228 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-11-18</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Steril</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Kärr med lövträd</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sofia Berg</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sofia Berg, Anders Esplund</t>
+          <t>Janolof Hermansson, Stig-Åke Svenson, Cecilia Rastad, Åke Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136980578</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136980141</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80602</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Dövensberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>535927</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6672084</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>örtrikt nedanför brant med mossiga klippor</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>skogslind</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Tilia cordata</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Tilia cordata</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Stig-Åke Svenson, Cecilia Rastad, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136980141</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136976719</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58000</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100110</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gråspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picus canus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Dövensberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>535927</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6672034</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Avstånd cirka 80 meter.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Janolof Hermansson, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976719</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>98600589</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Smedjebacken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>536348</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6671865</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-11-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-11-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Anders Esplund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98600589</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136976735</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99257</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Dövensberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>535879</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6671949</v>
+      </c>
+      <c r="S10" t="n">
+        <v>26</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Janolof Hermansson, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976735</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136976710</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Dövensberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>535946</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6672101</v>
+      </c>
+      <c r="S11" t="n">
+        <v>18</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Janolof Hermansson, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976710</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136976716</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Dövensberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>535941</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6672054</v>
+      </c>
+      <c r="S12" t="n">
+        <v>12</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Janolof Hermansson, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976716</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136976720</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Dövensberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>535929</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6672035</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Janolof Hermansson, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976720</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136976721</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Dövensberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>535927</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6672048</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Janolof Hermansson, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976721</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136976722</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Dövensberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>535921</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6672061</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Janolof Hermansson, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976722</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136976726</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Dövensberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>535914</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6672084</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 2 dm hög blomstängel. Frodiga plantor.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Janolof Hermansson, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976726</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136976738</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98209</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Dövensberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>536193</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6671749</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Janolof Hermansson, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976738</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>98600591</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Smedjebacken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>536381</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6671830</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-11-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-11-18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Anders Esplund</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98600591</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>98600592</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Smedjebacken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>536385</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6671884</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-11-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-11-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Anders Esplund</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98600592</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>98600593</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Smedjebacken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>536389</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6671850</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-11-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-11-18</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Anders Esplund</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/98600593</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136976729</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98215</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Dövensberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>535866</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6672069</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Janolof Hermansson, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976729</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136976734</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98215</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Dövensberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>535880</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6671963</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Janolof Hermansson, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976734</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136976712</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Dövensberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>535937</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6672087</v>
+      </c>
+      <c r="S23" t="n">
+        <v>13</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Cirka m2.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Janolof Hermansson, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976712</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136976715</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Dövensberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>535943</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6672061</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Janolof Hermansson, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976715</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136981833</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Dövensberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>535939</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6672071</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson, Cecilia Rastad, Janolof Hermansson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136981833</t>
         </is>
       </c>
     </row>
@@ -1195,6 +3475,25 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -1479,7 +1479,7 @@
         <v>535927</v>
       </c>
       <c r="R8" t="n">
-        <v>6672034</v>
+        <v>6672033</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980670</v>
       </c>
       <c r="B2" t="n">
-        <v>92381</v>
+        <v>92383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136980386</v>
       </c>
       <c r="B4" t="n">
-        <v>81134</v>
+        <v>81138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>136980140</v>
       </c>
       <c r="B5" t="n">
-        <v>79732</v>
+        <v>79736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>136980578</v>
       </c>
       <c r="B6" t="n">
-        <v>79732</v>
+        <v>79736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>136980141</v>
       </c>
       <c r="B7" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>535927</v>
       </c>
       <c r="R8" t="n">
-        <v>6672033</v>
+        <v>6672034</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1663,7 +1663,7 @@
         <v>136976735</v>
       </c>
       <c r="B10" t="n">
-        <v>99257</v>
+        <v>99263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>136976710</v>
       </c>
       <c r="B11" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>136976716</v>
       </c>
       <c r="B12" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136976720</v>
       </c>
       <c r="B13" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136976721</v>
       </c>
       <c r="B14" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136976722</v>
       </c>
       <c r="B15" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136976726</v>
       </c>
       <c r="B16" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>136976738</v>
       </c>
       <c r="B17" t="n">
-        <v>98209</v>
+        <v>98215</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>136976729</v>
       </c>
       <c r="B21" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136976734</v>
       </c>
       <c r="B22" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>136976712</v>
       </c>
       <c r="B23" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>136976715</v>
       </c>
       <c r="B24" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136981833</v>
       </c>
       <c r="B25" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980670</v>
       </c>
       <c r="B2" t="n">
-        <v>92383</v>
+        <v>92385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136980386</v>
       </c>
       <c r="B4" t="n">
-        <v>81138</v>
+        <v>81140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>136980140</v>
       </c>
       <c r="B5" t="n">
-        <v>79736</v>
+        <v>79738</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>136980578</v>
       </c>
       <c r="B6" t="n">
-        <v>79736</v>
+        <v>79738</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>136980141</v>
       </c>
       <c r="B7" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136976735</v>
       </c>
       <c r="B10" t="n">
-        <v>99263</v>
+        <v>99265</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>136976710</v>
       </c>
       <c r="B11" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>136976716</v>
       </c>
       <c r="B12" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136976720</v>
       </c>
       <c r="B13" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136976721</v>
       </c>
       <c r="B14" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136976722</v>
       </c>
       <c r="B15" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136976726</v>
       </c>
       <c r="B16" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>136976738</v>
       </c>
       <c r="B17" t="n">
-        <v>98215</v>
+        <v>98217</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>136976729</v>
       </c>
       <c r="B21" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136976734</v>
       </c>
       <c r="B22" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>136976712</v>
       </c>
       <c r="B23" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>136976715</v>
       </c>
       <c r="B24" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136981833</v>
       </c>
       <c r="B25" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980670</v>
       </c>
       <c r="B2" t="n">
-        <v>92385</v>
+        <v>92386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136980386</v>
       </c>
       <c r="B4" t="n">
-        <v>81140</v>
+        <v>81141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>136980140</v>
       </c>
       <c r="B5" t="n">
-        <v>79738</v>
+        <v>79739</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>136980578</v>
       </c>
       <c r="B6" t="n">
-        <v>79738</v>
+        <v>79739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>136980141</v>
       </c>
       <c r="B7" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>535927</v>
       </c>
       <c r="R8" t="n">
-        <v>6672034</v>
+        <v>6672033</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1663,7 +1663,7 @@
         <v>136976735</v>
       </c>
       <c r="B10" t="n">
-        <v>99265</v>
+        <v>99266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>136976710</v>
       </c>
       <c r="B11" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>136976716</v>
       </c>
       <c r="B12" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136976720</v>
       </c>
       <c r="B13" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136976721</v>
       </c>
       <c r="B14" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136976722</v>
       </c>
       <c r="B15" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136976726</v>
       </c>
       <c r="B16" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>136976738</v>
       </c>
       <c r="B17" t="n">
-        <v>98217</v>
+        <v>98218</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>136976729</v>
       </c>
       <c r="B21" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136976734</v>
       </c>
       <c r="B22" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>136976712</v>
       </c>
       <c r="B23" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>136976715</v>
       </c>
       <c r="B24" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136981833</v>
       </c>
       <c r="B25" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -1479,7 +1479,7 @@
         <v>535927</v>
       </c>
       <c r="R8" t="n">
-        <v>6672033</v>
+        <v>6672034</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980670</v>
       </c>
       <c r="B2" t="n">
-        <v>92386</v>
+        <v>92392</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>535927</v>
       </c>
       <c r="R8" t="n">
-        <v>6672034</v>
+        <v>6672033</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1663,7 +1663,7 @@
         <v>136976735</v>
       </c>
       <c r="B10" t="n">
-        <v>99266</v>
+        <v>99272</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>136976710</v>
       </c>
       <c r="B11" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>136976716</v>
       </c>
       <c r="B12" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136976720</v>
       </c>
       <c r="B13" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136976721</v>
       </c>
       <c r="B14" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136976722</v>
       </c>
       <c r="B15" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136976726</v>
       </c>
       <c r="B16" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>136976738</v>
       </c>
       <c r="B17" t="n">
-        <v>98218</v>
+        <v>98224</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>136976729</v>
       </c>
       <c r="B21" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136976734</v>
       </c>
       <c r="B22" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>136976712</v>
       </c>
       <c r="B23" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>136976715</v>
       </c>
       <c r="B24" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136981833</v>
       </c>
       <c r="B25" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980670</v>
       </c>
       <c r="B2" t="n">
-        <v>92392</v>
+        <v>92396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136980386</v>
       </c>
       <c r="B4" t="n">
-        <v>81141</v>
+        <v>81143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>136980140</v>
       </c>
       <c r="B5" t="n">
-        <v>79739</v>
+        <v>79741</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>136980578</v>
       </c>
       <c r="B6" t="n">
-        <v>79739</v>
+        <v>79741</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>136980141</v>
       </c>
       <c r="B7" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136976735</v>
       </c>
       <c r="B10" t="n">
-        <v>99272</v>
+        <v>99276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>136976710</v>
       </c>
       <c r="B11" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>136976716</v>
       </c>
       <c r="B12" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136976720</v>
       </c>
       <c r="B13" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136976721</v>
       </c>
       <c r="B14" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136976722</v>
       </c>
       <c r="B15" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136976726</v>
       </c>
       <c r="B16" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>136976738</v>
       </c>
       <c r="B17" t="n">
-        <v>98224</v>
+        <v>98228</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>136976729</v>
       </c>
       <c r="B21" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136976734</v>
       </c>
       <c r="B22" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>136976712</v>
       </c>
       <c r="B23" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>136976715</v>
       </c>
       <c r="B24" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136981833</v>
       </c>
       <c r="B25" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -1479,7 +1479,7 @@
         <v>535927</v>
       </c>
       <c r="R8" t="n">
-        <v>6672033</v>
+        <v>6672034</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1663,7 +1663,7 @@
         <v>136976735</v>
       </c>
       <c r="B10" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>136976710</v>
       </c>
       <c r="B11" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>136976716</v>
       </c>
       <c r="B12" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136976720</v>
       </c>
       <c r="B13" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136976721</v>
       </c>
       <c r="B14" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136976722</v>
       </c>
       <c r="B15" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136976726</v>
       </c>
       <c r="B16" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>136976738</v>
       </c>
       <c r="B17" t="n">
-        <v>98228</v>
+        <v>98230</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>136976729</v>
       </c>
       <c r="B21" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136976734</v>
       </c>
       <c r="B22" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>136976712</v>
       </c>
       <c r="B23" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>136976715</v>
       </c>
       <c r="B24" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136981833</v>
       </c>
       <c r="B25" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980670</v>
       </c>
       <c r="B2" t="n">
-        <v>92396</v>
+        <v>92398</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136980386</v>
       </c>
       <c r="B4" t="n">
-        <v>81143</v>
+        <v>81146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>136980140</v>
       </c>
       <c r="B5" t="n">
-        <v>79741</v>
+        <v>79744</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>136980578</v>
       </c>
       <c r="B6" t="n">
-        <v>79741</v>
+        <v>79744</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>136980141</v>
       </c>
       <c r="B7" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>535927</v>
       </c>
       <c r="R8" t="n">
-        <v>6672034</v>
+        <v>6672033</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1663,7 +1663,7 @@
         <v>136976735</v>
       </c>
       <c r="B10" t="n">
-        <v>99278</v>
+        <v>99280</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>136976710</v>
       </c>
       <c r="B11" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>136976716</v>
       </c>
       <c r="B12" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136976720</v>
       </c>
       <c r="B13" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136976721</v>
       </c>
       <c r="B14" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136976722</v>
       </c>
       <c r="B15" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136976726</v>
       </c>
       <c r="B16" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>136976738</v>
       </c>
       <c r="B17" t="n">
-        <v>98230</v>
+        <v>98232</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>136976729</v>
       </c>
       <c r="B21" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136976734</v>
       </c>
       <c r="B22" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>136976712</v>
       </c>
       <c r="B23" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>136976715</v>
       </c>
       <c r="B24" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136981833</v>
       </c>
       <c r="B25" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980670</v>
       </c>
       <c r="B2" t="n">
-        <v>92398</v>
+        <v>92411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136980386</v>
       </c>
       <c r="B4" t="n">
-        <v>81146</v>
+        <v>81159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>136980140</v>
       </c>
       <c r="B5" t="n">
-        <v>79744</v>
+        <v>79757</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>136980578</v>
       </c>
       <c r="B6" t="n">
-        <v>79744</v>
+        <v>79757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>136980141</v>
       </c>
       <c r="B7" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>136976719</v>
       </c>
       <c r="B8" t="n">
-        <v>58000</v>
+        <v>58013</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136976735</v>
       </c>
       <c r="B10" t="n">
-        <v>99280</v>
+        <v>99293</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>136976710</v>
       </c>
       <c r="B11" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>136976716</v>
       </c>
       <c r="B12" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136976720</v>
       </c>
       <c r="B13" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136976721</v>
       </c>
       <c r="B14" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136976722</v>
       </c>
       <c r="B15" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136976726</v>
       </c>
       <c r="B16" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>136976738</v>
       </c>
       <c r="B17" t="n">
-        <v>98232</v>
+        <v>98245</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>136976729</v>
       </c>
       <c r="B21" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136976734</v>
       </c>
       <c r="B22" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>136976712</v>
       </c>
       <c r="B23" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>136976715</v>
       </c>
       <c r="B24" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136981833</v>
       </c>
       <c r="B25" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980670</v>
       </c>
       <c r="B2" t="n">
-        <v>92411</v>
+        <v>92413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136980386</v>
       </c>
       <c r="B4" t="n">
-        <v>81159</v>
+        <v>81161</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>136980140</v>
       </c>
       <c r="B5" t="n">
-        <v>79757</v>
+        <v>79759</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>136980578</v>
       </c>
       <c r="B6" t="n">
-        <v>79757</v>
+        <v>79759</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>136980141</v>
       </c>
       <c r="B7" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>136976719</v>
       </c>
       <c r="B8" t="n">
-        <v>58013</v>
+        <v>58015</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136976735</v>
       </c>
       <c r="B10" t="n">
-        <v>99293</v>
+        <v>99295</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>136976710</v>
       </c>
       <c r="B11" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>136976716</v>
       </c>
       <c r="B12" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136976720</v>
       </c>
       <c r="B13" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136976721</v>
       </c>
       <c r="B14" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136976722</v>
       </c>
       <c r="B15" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136976726</v>
       </c>
       <c r="B16" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>136976738</v>
       </c>
       <c r="B17" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>136976729</v>
       </c>
       <c r="B21" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136976734</v>
       </c>
       <c r="B22" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>136976712</v>
       </c>
       <c r="B23" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>136976715</v>
       </c>
       <c r="B24" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136981833</v>
       </c>
       <c r="B25" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980670</v>
       </c>
       <c r="B2" t="n">
-        <v>92413</v>
+        <v>92416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136976735</v>
       </c>
       <c r="B10" t="n">
-        <v>99295</v>
+        <v>99298</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>136976710</v>
       </c>
       <c r="B11" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>136976716</v>
       </c>
       <c r="B12" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136976720</v>
       </c>
       <c r="B13" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136976721</v>
       </c>
       <c r="B14" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136976722</v>
       </c>
       <c r="B15" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136976726</v>
       </c>
       <c r="B16" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>136976738</v>
       </c>
       <c r="B17" t="n">
-        <v>98247</v>
+        <v>98250</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>136976729</v>
       </c>
       <c r="B21" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136976734</v>
       </c>
       <c r="B22" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>136976712</v>
       </c>
       <c r="B23" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>136976715</v>
       </c>
       <c r="B24" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136981833</v>
       </c>
       <c r="B25" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980670</v>
       </c>
       <c r="B2" t="n">
-        <v>92416</v>
+        <v>92426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136980386</v>
       </c>
       <c r="B4" t="n">
-        <v>81161</v>
+        <v>81171</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>136980140</v>
       </c>
       <c r="B5" t="n">
-        <v>79759</v>
+        <v>79769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>136980578</v>
       </c>
       <c r="B6" t="n">
-        <v>79759</v>
+        <v>79769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>136980141</v>
       </c>
       <c r="B7" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>136976719</v>
       </c>
       <c r="B8" t="n">
-        <v>58015</v>
+        <v>58025</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136976735</v>
       </c>
       <c r="B10" t="n">
-        <v>99298</v>
+        <v>99308</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>136976710</v>
       </c>
       <c r="B11" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>136976716</v>
       </c>
       <c r="B12" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136976720</v>
       </c>
       <c r="B13" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136976721</v>
       </c>
       <c r="B14" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136976722</v>
       </c>
       <c r="B15" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136976726</v>
       </c>
       <c r="B16" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>136976738</v>
       </c>
       <c r="B17" t="n">
-        <v>98250</v>
+        <v>98260</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>136976729</v>
       </c>
       <c r="B21" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136976734</v>
       </c>
       <c r="B22" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>136976712</v>
       </c>
       <c r="B23" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>136976715</v>
       </c>
       <c r="B24" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136981833</v>
       </c>
       <c r="B25" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980670</v>
       </c>
       <c r="B2" t="n">
-        <v>92426</v>
+        <v>92427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136976735</v>
       </c>
       <c r="B10" t="n">
-        <v>99308</v>
+        <v>99309</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>136976710</v>
       </c>
       <c r="B11" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>136976716</v>
       </c>
       <c r="B12" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136976720</v>
       </c>
       <c r="B13" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136976721</v>
       </c>
       <c r="B14" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136976722</v>
       </c>
       <c r="B15" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136976726</v>
       </c>
       <c r="B16" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>136976738</v>
       </c>
       <c r="B17" t="n">
-        <v>98260</v>
+        <v>98261</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>136976729</v>
       </c>
       <c r="B21" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136976734</v>
       </c>
       <c r="B22" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>136976712</v>
       </c>
       <c r="B23" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>136976715</v>
       </c>
       <c r="B24" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136981833</v>
       </c>
       <c r="B25" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980670</v>
       </c>
       <c r="B2" t="n">
-        <v>92427</v>
+        <v>92430</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136980386</v>
       </c>
       <c r="B4" t="n">
-        <v>81171</v>
+        <v>81174</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>136980140</v>
       </c>
       <c r="B5" t="n">
-        <v>79769</v>
+        <v>79772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>136980578</v>
       </c>
       <c r="B6" t="n">
-        <v>79769</v>
+        <v>79772</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>136980141</v>
       </c>
       <c r="B7" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>136976719</v>
       </c>
       <c r="B8" t="n">
-        <v>58025</v>
+        <v>58026</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>535927</v>
       </c>
       <c r="R8" t="n">
-        <v>6672033</v>
+        <v>6672034</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1663,7 +1663,7 @@
         <v>136976735</v>
       </c>
       <c r="B10" t="n">
-        <v>99309</v>
+        <v>99314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>136976710</v>
       </c>
       <c r="B11" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>136976716</v>
       </c>
       <c r="B12" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136976720</v>
       </c>
       <c r="B13" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136976721</v>
       </c>
       <c r="B14" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136976722</v>
       </c>
       <c r="B15" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136976726</v>
       </c>
       <c r="B16" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>136976738</v>
       </c>
       <c r="B17" t="n">
-        <v>98261</v>
+        <v>98266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>136976729</v>
       </c>
       <c r="B21" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136976734</v>
       </c>
       <c r="B22" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>136976712</v>
       </c>
       <c r="B23" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>136976715</v>
       </c>
       <c r="B24" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136981833</v>
       </c>
       <c r="B25" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980670</v>
       </c>
       <c r="B2" t="n">
-        <v>92430</v>
+        <v>92432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>535927</v>
       </c>
       <c r="R8" t="n">
-        <v>6672034</v>
+        <v>6672033</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1663,7 +1663,7 @@
         <v>136976735</v>
       </c>
       <c r="B10" t="n">
-        <v>99314</v>
+        <v>99316</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>136976710</v>
       </c>
       <c r="B11" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>136976716</v>
       </c>
       <c r="B12" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136976720</v>
       </c>
       <c r="B13" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136976721</v>
       </c>
       <c r="B14" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136976722</v>
       </c>
       <c r="B15" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136976726</v>
       </c>
       <c r="B16" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>136976738</v>
       </c>
       <c r="B17" t="n">
-        <v>98266</v>
+        <v>98268</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>136976729</v>
       </c>
       <c r="B21" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136976734</v>
       </c>
       <c r="B22" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>136976712</v>
       </c>
       <c r="B23" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>136976715</v>
       </c>
       <c r="B24" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136981833</v>
       </c>
       <c r="B25" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980670</v>
       </c>
       <c r="B2" t="n">
-        <v>92432</v>
+        <v>92437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136980386</v>
       </c>
       <c r="B4" t="n">
-        <v>81174</v>
+        <v>81179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>136980140</v>
       </c>
       <c r="B5" t="n">
-        <v>79772</v>
+        <v>79777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>136980578</v>
       </c>
       <c r="B6" t="n">
-        <v>79772</v>
+        <v>79777</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>136980141</v>
       </c>
       <c r="B7" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>136976719</v>
       </c>
       <c r="B8" t="n">
-        <v>58026</v>
+        <v>58027</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136976735</v>
       </c>
       <c r="B10" t="n">
-        <v>99316</v>
+        <v>99322</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>136976710</v>
       </c>
       <c r="B11" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>136976716</v>
       </c>
       <c r="B12" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136976720</v>
       </c>
       <c r="B13" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136976721</v>
       </c>
       <c r="B14" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136976722</v>
       </c>
       <c r="B15" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136976726</v>
       </c>
       <c r="B16" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>136976738</v>
       </c>
       <c r="B17" t="n">
-        <v>98268</v>
+        <v>98274</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>136976729</v>
       </c>
       <c r="B21" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136976734</v>
       </c>
       <c r="B22" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>136976712</v>
       </c>
       <c r="B23" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>136976715</v>
       </c>
       <c r="B24" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136981833</v>
       </c>
       <c r="B25" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980670</v>
       </c>
       <c r="B2" t="n">
-        <v>92437</v>
+        <v>92449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136980386</v>
       </c>
       <c r="B4" t="n">
-        <v>81179</v>
+        <v>81190</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>136980140</v>
       </c>
       <c r="B5" t="n">
-        <v>79777</v>
+        <v>79788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>136980578</v>
       </c>
       <c r="B6" t="n">
-        <v>79777</v>
+        <v>79788</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>136980141</v>
       </c>
       <c r="B7" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136976735</v>
       </c>
       <c r="B10" t="n">
-        <v>99322</v>
+        <v>99334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>136976710</v>
       </c>
       <c r="B11" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>136976716</v>
       </c>
       <c r="B12" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136976720</v>
       </c>
       <c r="B13" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136976721</v>
       </c>
       <c r="B14" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136976722</v>
       </c>
       <c r="B15" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136976726</v>
       </c>
       <c r="B16" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>136976738</v>
       </c>
       <c r="B17" t="n">
-        <v>98274</v>
+        <v>98286</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>136976729</v>
       </c>
       <c r="B21" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136976734</v>
       </c>
       <c r="B22" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>136976712</v>
       </c>
       <c r="B23" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>136976715</v>
       </c>
       <c r="B24" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136981833</v>
       </c>
       <c r="B25" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980670</v>
       </c>
       <c r="B2" t="n">
-        <v>92449</v>
+        <v>92450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136980386</v>
       </c>
       <c r="B4" t="n">
-        <v>81190</v>
+        <v>81191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>136980140</v>
       </c>
       <c r="B5" t="n">
-        <v>79788</v>
+        <v>79789</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>136980578</v>
       </c>
       <c r="B6" t="n">
-        <v>79788</v>
+        <v>79789</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>136980141</v>
       </c>
       <c r="B7" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136976735</v>
       </c>
       <c r="B10" t="n">
-        <v>99334</v>
+        <v>99335</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>136976710</v>
       </c>
       <c r="B11" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>136976716</v>
       </c>
       <c r="B12" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136976720</v>
       </c>
       <c r="B13" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136976721</v>
       </c>
       <c r="B14" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136976722</v>
       </c>
       <c r="B15" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136976726</v>
       </c>
       <c r="B16" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>136976738</v>
       </c>
       <c r="B17" t="n">
-        <v>98286</v>
+        <v>98287</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>136976729</v>
       </c>
       <c r="B21" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136976734</v>
       </c>
       <c r="B22" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>136976712</v>
       </c>
       <c r="B23" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>136976715</v>
       </c>
       <c r="B24" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136981833</v>
       </c>
       <c r="B25" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980670</v>
       </c>
       <c r="B2" t="n">
-        <v>92450</v>
+        <v>92453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136980386</v>
       </c>
       <c r="B4" t="n">
-        <v>81191</v>
+        <v>81193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>136980140</v>
       </c>
       <c r="B5" t="n">
-        <v>79789</v>
+        <v>79791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>136980578</v>
       </c>
       <c r="B6" t="n">
-        <v>79789</v>
+        <v>79791</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>136980141</v>
       </c>
       <c r="B7" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>535927</v>
       </c>
       <c r="R8" t="n">
-        <v>6672033</v>
+        <v>6672034</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1663,7 +1663,7 @@
         <v>136976735</v>
       </c>
       <c r="B10" t="n">
-        <v>99335</v>
+        <v>99338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>136976710</v>
       </c>
       <c r="B11" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>136976716</v>
       </c>
       <c r="B12" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136976720</v>
       </c>
       <c r="B13" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136976721</v>
       </c>
       <c r="B14" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136976722</v>
       </c>
       <c r="B15" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136976726</v>
       </c>
       <c r="B16" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>136976738</v>
       </c>
       <c r="B17" t="n">
-        <v>98287</v>
+        <v>98290</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>136976729</v>
       </c>
       <c r="B21" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136976734</v>
       </c>
       <c r="B22" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>136976712</v>
       </c>
       <c r="B23" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>136976715</v>
       </c>
       <c r="B24" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136981833</v>
       </c>
       <c r="B25" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980670</v>
       </c>
       <c r="B2" t="n">
-        <v>92453</v>
+        <v>92454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136980386</v>
       </c>
       <c r="B4" t="n">
-        <v>81193</v>
+        <v>81194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>136980140</v>
       </c>
       <c r="B5" t="n">
-        <v>79791</v>
+        <v>79792</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>136980578</v>
       </c>
       <c r="B6" t="n">
-        <v>79791</v>
+        <v>79792</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>136980141</v>
       </c>
       <c r="B7" t="n">
-        <v>80661</v>
+        <v>80662</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>535927</v>
       </c>
       <c r="R8" t="n">
-        <v>6672033</v>
+        <v>6672034</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1663,7 +1663,7 @@
         <v>136976735</v>
       </c>
       <c r="B10" t="n">
-        <v>99338</v>
+        <v>99339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>136976710</v>
       </c>
       <c r="B11" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>136976716</v>
       </c>
       <c r="B12" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136976720</v>
       </c>
       <c r="B13" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136976721</v>
       </c>
       <c r="B14" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136976722</v>
       </c>
       <c r="B15" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136976726</v>
       </c>
       <c r="B16" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>136976738</v>
       </c>
       <c r="B17" t="n">
-        <v>98290</v>
+        <v>98291</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>136976729</v>
       </c>
       <c r="B21" t="n">
-        <v>98296</v>
+        <v>98297</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136976734</v>
       </c>
       <c r="B22" t="n">
-        <v>98296</v>
+        <v>98297</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>136976712</v>
       </c>
       <c r="B23" t="n">
-        <v>101650</v>
+        <v>101651</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>136976715</v>
       </c>
       <c r="B24" t="n">
-        <v>101650</v>
+        <v>101651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136981833</v>
       </c>
       <c r="B25" t="n">
-        <v>101650</v>
+        <v>101651</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2026 artfynd.xlsx
+++ b/artfynd/A 38991-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980670</v>
       </c>
       <c r="B2" t="n">
-        <v>92454</v>
+        <v>92457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136980386</v>
       </c>
       <c r="B4" t="n">
-        <v>81194</v>
+        <v>81197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>136980140</v>
       </c>
       <c r="B5" t="n">
-        <v>79792</v>
+        <v>79795</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>136980578</v>
       </c>
       <c r="B6" t="n">
-        <v>79792</v>
+        <v>79795</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>136980141</v>
       </c>
       <c r="B7" t="n">
-        <v>80662</v>
+        <v>80665</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>136976719</v>
       </c>
       <c r="B8" t="n">
-        <v>58027</v>
+        <v>58030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>535927</v>
       </c>
       <c r="R8" t="n">
-        <v>6672034</v>
+        <v>6672033</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1663,7 +1663,7 @@
         <v>136976735</v>
       </c>
       <c r="B10" t="n">
-        <v>99339</v>
+        <v>99342</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>136976710</v>
       </c>
       <c r="B11" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>136976716</v>
       </c>
       <c r="B12" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136976720</v>
       </c>
       <c r="B13" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136976721</v>
       </c>
       <c r="B14" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136976722</v>
       </c>
       <c r="B15" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>136976726</v>
       </c>
       <c r="B16" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>136976738</v>
       </c>
       <c r="B17" t="n">
-        <v>98291</v>
+        <v>98294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>136976729</v>
       </c>
       <c r="B21" t="n">
-        <v>98297</v>
+        <v>98300</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136976734</v>
       </c>
       <c r="B22" t="n">
-        <v>98297</v>
+        <v>98300</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>136976712</v>
       </c>
       <c r="B23" t="n">
-        <v>101651</v>
+        <v>101654</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>136976715</v>
       </c>
       <c r="B24" t="n">
-        <v>101651</v>
+        <v>101654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136981833</v>
       </c>
       <c r="B25" t="n">
-        <v>101651</v>
+        <v>101654</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
